--- a/artfynd/A 73598-2021 artfynd.xlsx
+++ b/artfynd/A 73598-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73598-2021 artfynd.xlsx
+++ b/artfynd/A 73598-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65281392</v>
+        <v>65281395</v>
       </c>
       <c r="B2" t="n">
-        <v>85253</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>720</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591759.8800075976</v>
+        <v>591807</v>
       </c>
       <c r="R2" t="n">
-        <v>6669556.05217061</v>
+        <v>6669504</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-09-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-09-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-07-25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,53 +775,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65281348</v>
+        <v>65281405</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>788</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vivastbo, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591756.8881365533</v>
+        <v>591810</v>
       </c>
       <c r="R3" t="n">
-        <v>6669555.977291703</v>
+        <v>6669507</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,6 +856,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,6 +872,306 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>65281392</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>591760</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6669556</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-09-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-09-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>65281353</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>591801</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6669509</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-07-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-07-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>65281348</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vivastbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>591757</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6669556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Möklinta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-07-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-07-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Henrik Berg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 73598-2021 artfynd.xlsx
+++ b/artfynd/A 73598-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281395</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281405</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281392</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281353</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,8 +1197,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65281348</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>